--- a/input_files/Untitled spreadsheet.xlsx
+++ b/input_files/Untitled spreadsheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9840" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9840"/>
   </bookViews>
   <sheets>
     <sheet name="Dad_config" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <t>dag_1</t>
   </si>
   <si>
-    <t>My_first_dag</t>
+    <t>My_first_dag_test</t>
   </si>
   <si>
     <t>Manual</t>
@@ -77,7 +77,7 @@
     <t>dag_2</t>
   </si>
   <si>
-    <t>My_second_dag</t>
+    <t>My_second_dag_test</t>
   </si>
   <si>
     <t>Preset</t>
@@ -1265,6 +1265,8 @@
   <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="24.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="31.3333333333333" customWidth="1"/>
     <col min="6" max="6" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>

--- a/input_files/Untitled spreadsheet.xlsx
+++ b/input_files/Untitled spreadsheet.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t>dad_ref</t>
   </si>
@@ -65,25 +65,25 @@
     <t>null</t>
   </si>
   <si>
+    <t>start_date: 2026-01-02,owner:amir</t>
+  </si>
+  <si>
+    <t>My first demo dag</t>
+  </si>
+  <si>
+    <t>dag_2</t>
+  </si>
+  <si>
+    <t>My_second_dag_test</t>
+  </si>
+  <si>
+    <t>cron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* * * * </t>
+  </si>
+  <si>
     <t>start_date: 2026-01-01,owner:airflow</t>
-  </si>
-  <si>
-    <t>catchup:false</t>
-  </si>
-  <si>
-    <t>My first demo dag</t>
-  </si>
-  <si>
-    <t>dag_2</t>
-  </si>
-  <si>
-    <t>My_second_dag_test</t>
-  </si>
-  <si>
-    <t>Preset</t>
-  </si>
-  <si>
-    <t>daily</t>
   </si>
   <si>
     <t>my_second_demo_dag</t>
@@ -1309,32 +1309,28 @@
       <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:7">
       <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1427,7 +1423,7 @@
     </row>
     <row r="5" customHeight="1" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -1503,7 +1499,7 @@
     </row>
     <row r="5" customHeight="1" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>33</v>
